--- a/product_selector_out/STM8L151-152.xlsx
+++ b/product_selector_out/STM8L151-152.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG37"/>
+  <dimension ref="A1:AH37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,8 @@
     <col width="23.46484375" customWidth="1" min="30" max="30"/>
     <col width="11.6328125" customWidth="1" min="31" max="31"/>
     <col width="43.6484375" customWidth="1" min="32" max="32"/>
-    <col width="52" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="52" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -710,6 +711,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -877,6 +883,11 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -1044,6 +1055,11 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -1211,6 +1227,11 @@
       </c>
       <c r="AG13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -1378,6 +1399,11 @@
       </c>
       <c r="AG14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -1545,6 +1571,11 @@
       </c>
       <c r="AG15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -1712,6 +1743,11 @@
       </c>
       <c r="AG16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -1879,6 +1915,11 @@
       </c>
       <c r="AG17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151r6.pdf</t>
         </is>
       </c>
@@ -2046,6 +2087,11 @@
       </c>
       <c r="AG18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -2213,6 +2259,11 @@
       </c>
       <c r="AG19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -2380,6 +2431,11 @@
       </c>
       <c r="AG20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -2547,6 +2603,11 @@
       </c>
       <c r="AG21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -2714,6 +2775,11 @@
       </c>
       <c r="AG22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -2881,6 +2947,11 @@
       </c>
       <c r="AG23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -3048,6 +3119,11 @@
       </c>
       <c r="AG24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -3215,6 +3291,11 @@
       </c>
       <c r="AG25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -3382,6 +3463,11 @@
       </c>
       <c r="AG26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -3549,6 +3635,11 @@
       </c>
       <c r="AG27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -3716,6 +3807,11 @@
       </c>
       <c r="AG28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -3883,6 +3979,11 @@
       </c>
       <c r="AG29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -4050,6 +4151,11 @@
       </c>
       <c r="AG30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -4217,6 +4323,11 @@
       </c>
       <c r="AG31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -4384,6 +4495,11 @@
       </c>
       <c r="AG32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c4.pdf</t>
         </is>
       </c>
@@ -4551,6 +4667,11 @@
       </c>
       <c r="AG33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -4718,6 +4839,11 @@
       </c>
       <c r="AG34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -4885,6 +5011,11 @@
       </c>
       <c r="AG35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -5052,6 +5183,11 @@
       </c>
       <c r="AG36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
@@ -5219,14 +5355,19 @@
       </c>
       <c r="AG37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8l151c2.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
@@ -5268,7 +5409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG37"/>
+  <dimension ref="A1:AH37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5304,6 +5445,7 @@
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
     <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5490,6 +5632,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -5655,7 +5802,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG11" s="6" t="inlineStr">
+      <c r="AG11" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5822,7 +5974,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG12" s="6" t="inlineStr">
+      <c r="AG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5989,7 +6146,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG13" s="6" t="inlineStr">
+      <c r="AG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6156,7 +6318,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG14" s="6" t="inlineStr">
+      <c r="AG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6323,7 +6490,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG15" s="6" t="inlineStr">
+      <c r="AG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6490,7 +6662,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG16" s="6" t="inlineStr">
+      <c r="AG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6657,7 +6834,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG17" s="6" t="inlineStr">
+      <c r="AG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6824,7 +7006,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG18" s="6" t="inlineStr">
+      <c r="AG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6991,7 +7178,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG19" s="6" t="inlineStr">
+      <c r="AG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7158,7 +7350,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG20" s="6" t="inlineStr">
+      <c r="AG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7325,7 +7522,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG21" s="6" t="inlineStr">
+      <c r="AG21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7492,7 +7694,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG22" s="6" t="inlineStr">
+      <c r="AG22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7659,7 +7866,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG23" s="6" t="inlineStr">
+      <c r="AG23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7826,7 +8038,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG24" s="6" t="inlineStr">
+      <c r="AG24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7993,7 +8210,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG25" s="6" t="inlineStr">
+      <c r="AG25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8160,7 +8382,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG26" s="6" t="inlineStr">
+      <c r="AG26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8327,7 +8554,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG27" s="6" t="inlineStr">
+      <c r="AG27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8494,7 +8726,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG28" s="6" t="inlineStr">
+      <c r="AG28" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8661,7 +8898,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG29" s="6" t="inlineStr">
+      <c r="AG29" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8828,7 +9070,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG30" s="6" t="inlineStr">
+      <c r="AG30" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8995,7 +9242,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG31" s="6" t="inlineStr">
+      <c r="AG31" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9162,7 +9414,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG32" s="6" t="inlineStr">
+      <c r="AG32" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9329,7 +9586,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG33" s="6" t="inlineStr">
+      <c r="AG33" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9496,7 +9758,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG34" s="6" t="inlineStr">
+      <c r="AG34" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9663,7 +9930,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG35" s="6" t="inlineStr">
+      <c r="AG35" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9830,7 +10102,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG36" s="6" t="inlineStr">
+      <c r="AG36" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9997,7 +10274,12 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AG37" s="6" t="inlineStr">
+      <c r="AG37" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10005,8 +10287,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
